--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Fly Agaric Hat + Minecraft soil</v>
+        <v>Hachiware</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Hachiware</v>
+        <v>Pyramid Boss/Kolmisilmän Koipi</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Pyramid Boss/Kolmisilmän Koipi</v>
+        <v>Chit</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Chit</v>
+        <v>Hat hat</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Hat hat</v>
+        <v>Perry the Platypus Hat</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Perry the Platypus Hat</v>
+        <v>Ooze Head</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ooze Head</v>
+        <v>Bora Headpiece</v>
       </c>
     </row>
   </sheetData>

--- a/public/sheets/dunkbin_next_cosmetic_name.xlsx
+++ b/public/sheets/dunkbin_next_cosmetic_name.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Bora Headpiece</v>
+        <v>Dr. Beanies</v>
       </c>
     </row>
   </sheetData>
